--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569229859</v>
+        <v>46157.93101343153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101343153</v>
+        <v>46157.9317480687</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9317480687</v>
+        <v>46157.93400913757</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400913757</v>
+        <v>46157.93718854447</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718854447</v>
+        <v>46158.28217091735</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217091735</v>
+        <v>46158.29682629668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682629668</v>
+        <v>46158.29815635513</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815635513</v>
+        <v>46158.33388095863</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388095863</v>
+        <v>46158.36857913257</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857913257</v>
+        <v>46158.37288536246</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
